--- a/src/test/resources/vtiger-excel-data.xlsx
+++ b/src/test/resources/vtiger-excel-data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="31">
   <si>
     <t>TC_ID</t>
   </si>

--- a/src/test/resources/vtiger-excel-data.xlsx
+++ b/src/test/resources/vtiger-excel-data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="31">
   <si>
     <t>TC_ID</t>
   </si>
